--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="60">
   <si>
     <t>Problem Name</t>
   </si>
@@ -157,7 +157,7 @@
     <t>Track the lowest price so far, then update max profit each day</t>
   </si>
   <si>
-    <t>Sing Number</t>
+    <t>Single Number</t>
   </si>
   <si>
     <t>Array / Bit manipulation</t>
@@ -167,6 +167,30 @@
   </si>
   <si>
     <t>Xor cancels duplicate numbers and leaves the single number</t>
+  </si>
+  <si>
+    <t>Linked List Cycle</t>
+  </si>
+  <si>
+    <t>Linked List / Hash Table / Two Pointers</t>
+  </si>
+  <si>
+    <t>Forgot floyd's theorem</t>
+  </si>
+  <si>
+    <t>Use slow and fast pointers; if they meet then a cycle exists</t>
+  </si>
+  <si>
+    <t>Majority Element</t>
+  </si>
+  <si>
+    <t>Array / Hash Table / Counting</t>
+  </si>
+  <si>
+    <t>Counted frequencies with a hashmap instead of using boyer voting</t>
+  </si>
+  <si>
+    <t>Keep a candidate and counter. Majority elements survives cancellations</t>
   </si>
 </sst>
 </file>
@@ -714,25 +738,53 @@
       <c r="J11" s="3"/>
     </row>
     <row r="12">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
+      <c r="A12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
     </row>
     <row r="13">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+      <c r="A13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="74">
   <si>
     <t>Problem Name</t>
   </si>
@@ -191,6 +191,48 @@
   </si>
   <si>
     <t>Keep a candidate and counter. Majority elements survives cancellations</t>
+  </si>
+  <si>
+    <t>Reverse Linked List</t>
+  </si>
+  <si>
+    <t>Linked list/ Recursion</t>
+  </si>
+  <si>
+    <t>Lost track of pointers and overwrote next before saving it</t>
+  </si>
+  <si>
+    <t>Save next node first, reverse pointer, move both pointers forward.</t>
+  </si>
+  <si>
+    <t>Time: O(n), Space: O(1) iterative / O(n) recursive</t>
+  </si>
+  <si>
+    <t>Contains Duplicate</t>
+  </si>
+  <si>
+    <t>Array / Hash Table / Sorting</t>
+  </si>
+  <si>
+    <t>Tried nested loops instad of using a hash set</t>
+  </si>
+  <si>
+    <t>If a number is already in the set, duplicate found; otherwise add it</t>
+  </si>
+  <si>
+    <t>Time: O(n), Space: O(n) hash set / O(n log n), O(1) sorting</t>
+  </si>
+  <si>
+    <t>Remove Linked List elements</t>
+  </si>
+  <si>
+    <t>Linked List / Recursion</t>
+  </si>
+  <si>
+    <t>Forgot to handle removal of the head node and consecutive target values</t>
+  </si>
+  <si>
+    <t>Use a dummy node before head; if current value = target, skip the node</t>
   </si>
 </sst>
 </file>
@@ -790,37 +832,75 @@
       <c r="J13" s="3"/>
     </row>
     <row r="14">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
+      <c r="A14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
     </row>
     <row r="15">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
+      <c r="A15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
+      <c r="E15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
     </row>
     <row r="16">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+      <c r="A16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="88">
   <si>
     <t>Problem Name</t>
   </si>
@@ -229,10 +229,52 @@
     <t>Linked List / Recursion</t>
   </si>
   <si>
-    <t>Forgot to handle removal of the head node and consecutive target values</t>
+    <t xml:space="preserve">Forgot to handle removal of the head node and consecutive target values </t>
   </si>
   <si>
     <t>Use a dummy node before head; if current value = target, skip the node</t>
+  </si>
+  <si>
+    <t>Invert Binary Tree</t>
+  </si>
+  <si>
+    <t>Tree / DFS / BFS / Binary Tree</t>
+  </si>
+  <si>
+    <t>Forgot to swap children at every node and recurse through the entire tree</t>
+  </si>
+  <si>
+    <t>Swap left and right child of every node, then recurse (or BFS) through both subtrees</t>
+  </si>
+  <si>
+    <t>Time: O(n), Space: O(h) DFS / O(n) BFS</t>
+  </si>
+  <si>
+    <t>Palindrome Linked List</t>
+  </si>
+  <si>
+    <t>Linked List / Two Pointers / Stack / Recursion</t>
+  </si>
+  <si>
+    <t>Compared values without finding the middle and reversing the second half</t>
+  </si>
+  <si>
+    <t>Use slow/fast pointers to find middle, reverse second half, compare both halves.</t>
+  </si>
+  <si>
+    <t>Meeting Room</t>
+  </si>
+  <si>
+    <t>Array / Sorting</t>
+  </si>
+  <si>
+    <t>Forgot to sort intervals before checking for overlaps</t>
+  </si>
+  <si>
+    <t>Sort by start time, then check if current start &lt; previous end</t>
+  </si>
+  <si>
+    <t>Time: O(n log n), Space: O(1) or O(n) depending on sorting implementation</t>
   </si>
 </sst>
 </file>
@@ -906,10 +948,73 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17">
-      <c r="A17" s="3"/>
+      <c r="A17" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="3"/>
+      <c r="A18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>87</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="96">
   <si>
     <t>Problem Name</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Complexity</t>
   </si>
   <si>
-    <t>Redo date</t>
-  </si>
-  <si>
     <t>Two sum</t>
   </si>
   <si>
@@ -275,6 +272,33 @@
   </si>
   <si>
     <t>Time: O(n log n), Space: O(1) or O(n) depending on sorting implementation</t>
+  </si>
+  <si>
+    <t>Binary Tree Paths</t>
+  </si>
+  <si>
+    <t>Tree / DFS / Backtracking / String</t>
+  </si>
+  <si>
+    <t>Forgot to backtrack path properly or handle leaf nodes correctly</t>
+  </si>
+  <si>
+    <t>Build path while traversing; when reaching a leaf, add completed path to answer.</t>
+  </si>
+  <si>
+    <t>Time: O(n), Space: O(h)</t>
+  </si>
+  <si>
+    <t>Missing Number</t>
+  </si>
+  <si>
+    <t>Array / Math / Bit manipulation</t>
+  </si>
+  <si>
+    <t>Used extra storage instead of mathematical formula/XOR trick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected sum - actual sum = missing number (or use XOR) </t>
   </si>
 </sst>
 </file>
@@ -560,54 +584,52 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="H1" s="1"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
@@ -615,25 +637,25 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -641,25 +663,25 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
@@ -667,25 +689,25 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -693,25 +715,25 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="G7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
@@ -719,25 +741,25 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="G8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -745,25 +767,25 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
@@ -771,25 +793,25 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="G10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
@@ -797,25 +819,25 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="G11" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
@@ -823,25 +845,25 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="G12" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -849,25 +871,25 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="G13" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
@@ -875,25 +897,25 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
@@ -901,21 +923,21 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
@@ -923,25 +945,25 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="G16" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
@@ -949,72 +971,360 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="G18" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G19" s="2" t="s">
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
         <v>87</v>
       </c>
+      <c r="B20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="105">
   <si>
     <t>Problem Name</t>
   </si>
@@ -299,6 +299,33 @@
   </si>
   <si>
     <t xml:space="preserve">Expected sum - actual sum = missing number (or use XOR) </t>
+  </si>
+  <si>
+    <t>Move zeroes</t>
+  </si>
+  <si>
+    <t>Array / Two Pointers</t>
+  </si>
+  <si>
+    <t>Tried shifting elements multiple times instead of using two pointers</t>
+  </si>
+  <si>
+    <t>Keep a pointer for the next non-zero position and swap as you traverse</t>
+  </si>
+  <si>
+    <t>Range sum query - immutable</t>
+  </si>
+  <si>
+    <t>Array / Prefix Sum/ Design</t>
+  </si>
+  <si>
+    <t>Recomputed sums for every query instead of preprocessing prefix sums</t>
+  </si>
+  <si>
+    <t>Store cumulative sums so each query becomes a subtraction</t>
+  </si>
+  <si>
+    <t>Time: O(n) preprocessing, O(1) query, Space: O(n)</t>
   </si>
 </sst>
 </file>
@@ -1087,23 +1114,51 @@
       <c r="H21" s="3"/>
     </row>
     <row r="22">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
+      <c r="A22" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="H22" s="3"/>
     </row>
     <row r="23">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
+      <c r="A23" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>104</v>
+      </c>
       <c r="H23" s="3"/>
     </row>
     <row r="24">

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="113">
   <si>
     <t>Problem Name</t>
   </si>
@@ -326,6 +326,30 @@
   </si>
   <si>
     <t>Time: O(n) preprocessing, O(1) query, Space: O(n)</t>
+  </si>
+  <si>
+    <t>Counting Bits</t>
+  </si>
+  <si>
+    <t>Dynamic Programming / Bit Manipulation</t>
+  </si>
+  <si>
+    <t>Counted bits separately for every number instead of reusing previous answers</t>
+  </si>
+  <si>
+    <t>dp[i] = dp[i &gt;&gt; 1] + (i &amp; 1)</t>
+  </si>
+  <si>
+    <t>Is Subsequence</t>
+  </si>
+  <si>
+    <t>Two Pointers / String</t>
+  </si>
+  <si>
+    <t>Tried matching characters in the wrong order or used unnecessary nested loops</t>
+  </si>
+  <si>
+    <t>Move through both strings; advance subsequence pointer only when characters match</t>
   </si>
 </sst>
 </file>
@@ -1162,23 +1186,51 @@
       <c r="H23" s="3"/>
     </row>
     <row r="24">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
+      <c r="A24" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="H24" s="3"/>
     </row>
     <row r="25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
+      <c r="A25" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="H25" s="3"/>
     </row>
     <row r="26">

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="123">
   <si>
     <t>Problem Name</t>
   </si>
@@ -350,6 +350,36 @@
   </si>
   <si>
     <t>Move through both strings; advance subsequence pointer only when characters match</t>
+  </si>
+  <si>
+    <t>Find All Numbers Disappeared in an Array</t>
+  </si>
+  <si>
+    <t>Array / Hash Table</t>
+  </si>
+  <si>
+    <t>Used extra hash set instead of leveraging the input array for marking</t>
+  </si>
+  <si>
+    <t>Use index marking (negative marking) to record seen numbers</t>
+  </si>
+  <si>
+    <t>Time: O(n), Space: O(1) extra</t>
+  </si>
+  <si>
+    <t>Subtree of Another Tree</t>
+  </si>
+  <si>
+    <t>Tree / DFS / Binary Tree</t>
+  </si>
+  <si>
+    <t>Compared only root values instead of checking full subtree structure</t>
+  </si>
+  <si>
+    <t>For each node, check if trees are identical; otherwise search left and right subtrees</t>
+  </si>
+  <si>
+    <t>Time: O(m × n) worst case, Space: O(h)</t>
   </si>
 </sst>
 </file>
@@ -1234,23 +1264,51 @@
       <c r="H25" s="3"/>
     </row>
     <row r="26">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
+      <c r="A26" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="H26" s="3"/>
     </row>
     <row r="27">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
+      <c r="A27" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>122</v>
+      </c>
       <c r="H27" s="3"/>
     </row>
     <row r="28">

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="131">
   <si>
     <t>Problem Name</t>
   </si>
@@ -380,6 +380,30 @@
   </si>
   <si>
     <t>Time: O(m × n) worst case, Space: O(h)</t>
+  </si>
+  <si>
+    <t>Merge Two Binary Trees</t>
+  </si>
+  <si>
+    <t>Forgot to handle null nodes and merge corresponding nodes recursively</t>
+  </si>
+  <si>
+    <t>If both nodes exist, sum values and recurse; if one is null, return the other</t>
+  </si>
+  <si>
+    <t>Average of Levels in Binary Tree</t>
+  </si>
+  <si>
+    <t>Tree / BFS / DFS / Binary Tree</t>
+  </si>
+  <si>
+    <t>Calculated overall tree average instead of average per level</t>
+  </si>
+  <si>
+    <t>Process one level at a time and compute level sum ÷ level size</t>
+  </si>
+  <si>
+    <t>Time: O(n), Space: O(w) BFS</t>
   </si>
 </sst>
 </file>
@@ -1312,23 +1336,51 @@
       <c r="H27" s="3"/>
     </row>
     <row r="28">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
+      <c r="A28" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="H28" s="3"/>
     </row>
     <row r="29">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
+      <c r="A29" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>130</v>
+      </c>
       <c r="H29" s="3"/>
     </row>
     <row r="30">

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="140">
   <si>
     <t>Problem Name</t>
   </si>
@@ -404,6 +404,33 @@
   </si>
   <si>
     <t>Time: O(n), Space: O(w) BFS</t>
+  </si>
+  <si>
+    <t>Maximum Average Subarray I</t>
+  </si>
+  <si>
+    <t>Array / Sliding Window</t>
+  </si>
+  <si>
+    <t>Recalculated every subarray sum from scratch instead of updating the window</t>
+  </si>
+  <si>
+    <t>Keep a fixed-size window and update sum by adding new element and removing old element</t>
+  </si>
+  <si>
+    <t>Find Smallest Letter Greater Than Target</t>
+  </si>
+  <si>
+    <t>Array / Binary Search</t>
+  </si>
+  <si>
+    <t>Treated it like a linear search and forgot the array wraps around</t>
+  </si>
+  <si>
+    <t>Binary search for first element &gt; target; if none found, return first letter</t>
+  </si>
+  <si>
+    <t>Time: O(log n), Space: O(1)</t>
   </si>
 </sst>
 </file>
@@ -1384,23 +1411,51 @@
       <c r="H29" s="3"/>
     </row>
     <row r="30">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
+      <c r="A30" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="H30" s="3"/>
     </row>
     <row r="31">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
+      <c r="A31" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>139</v>
+      </c>
       <c r="H31" s="3"/>
     </row>
     <row r="32">

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="149">
   <si>
     <t>Problem Name</t>
   </si>
@@ -431,6 +431,33 @@
   </si>
   <si>
     <t>Time: O(log n), Space: O(1)</t>
+  </si>
+  <si>
+    <t>Binary Search</t>
+  </si>
+  <si>
+    <t>Used incorrect mid updates causing infinite loop or searched both halves unnecessarily</t>
+  </si>
+  <si>
+    <t>Compare target with middle and eliminate half the search space each iteration</t>
+  </si>
+  <si>
+    <t>Backspace String Compare</t>
+  </si>
+  <si>
+    <t>Two Pointers / String / Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Easy </t>
+  </si>
+  <si>
+    <t>Built entire processed strings instead of skipping deleted characters directly</t>
+  </si>
+  <si>
+    <t>Traverse from right to left and skip characters removed by backspaces</t>
+  </si>
+  <si>
+    <t>Time: O(n), Space: O(1) optimal</t>
   </si>
 </sst>
 </file>
@@ -1459,23 +1486,51 @@
       <c r="H31" s="3"/>
     </row>
     <row r="32">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
+      <c r="A32" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>139</v>
+      </c>
       <c r="H32" s="3"/>
     </row>
     <row r="33">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
+      <c r="A33" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="H33" s="3"/>
     </row>
     <row r="34">

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="157">
   <si>
     <t>Problem Name</t>
   </si>
@@ -458,6 +458,30 @@
   </si>
   <si>
     <t>Time: O(n), Space: O(1) optimal</t>
+  </si>
+  <si>
+    <t>Middle of the Linked List</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linked List / Two Pointers </t>
+  </si>
+  <si>
+    <t>Counted list length first instead of using slow/fast pointers</t>
+  </si>
+  <si>
+    <t>Slow moves 1 step, fast moves 2 steps; when fast reaches end, slow is at middle</t>
+  </si>
+  <si>
+    <t>Squares of a Sorted Array</t>
+  </si>
+  <si>
+    <t>Array / Two Pointers / Sorting</t>
+  </si>
+  <si>
+    <t>Squared then sorted instead of using the sorted property of the original array</t>
+  </si>
+  <si>
+    <t>Largest square comes from either end; fill result from back using two pointers</t>
   </si>
 </sst>
 </file>
@@ -1534,23 +1558,51 @@
       <c r="H33" s="3"/>
     </row>
     <row r="34">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
+      <c r="A34" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="H34" s="3"/>
     </row>
     <row r="35">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
+      <c r="A35" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="H35" s="3"/>
     </row>
     <row r="36">

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="167">
   <si>
     <t>Problem Name</t>
   </si>
@@ -482,6 +482,36 @@
   </si>
   <si>
     <t>Largest square comes from either end; fill result from back using two pointers</t>
+  </si>
+  <si>
+    <t>Index Pairs of a String</t>
+  </si>
+  <si>
+    <t>Array / String / Trie / Sorting</t>
+  </si>
+  <si>
+    <t>Checked every substring repeatedly instead of organizing words efficiently</t>
+  </si>
+  <si>
+    <t>For each starting position, find dictionary words that match and record intervals</t>
+  </si>
+  <si>
+    <t>Time: O(n × m) brute force / O(n × L) Trie, Space: O(total word length)</t>
+  </si>
+  <si>
+    <t>Convert 1D Array Into 2D Array</t>
+  </si>
+  <si>
+    <t>Array / Matrix / Simulation</t>
+  </si>
+  <si>
+    <t>Overcomplicated index calculations instead of filling row by row</t>
+  </si>
+  <si>
+    <t>Row = i / n, Column = i % n</t>
+  </si>
+  <si>
+    <t>Time: O(m × n), Space: O(m × n)</t>
   </si>
 </sst>
 </file>
@@ -1606,23 +1636,51 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
+      <c r="A36" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>161</v>
+      </c>
       <c r="H36" s="3"/>
     </row>
     <row r="37">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
+      <c r="A37" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>166</v>
+      </c>
       <c r="H37" s="3"/>
     </row>
     <row r="38">

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="175">
   <si>
     <t>Problem Name</t>
   </si>
@@ -512,6 +512,30 @@
   </si>
   <si>
     <t>Time: O(m × n), Space: O(m × n)</t>
+  </si>
+  <si>
+    <t>Valid Anagram</t>
+  </si>
+  <si>
+    <t>Hash Table / String / Sorting</t>
+  </si>
+  <si>
+    <t>Compared characters position-by-position instead of frequencies</t>
+  </si>
+  <si>
+    <t>Two strings are anagrams if character counts are identical</t>
+  </si>
+  <si>
+    <t>Time: O(n), Space: O(1) alphabet / O(n) general</t>
+  </si>
+  <si>
+    <t>Valid Palindrome</t>
+  </si>
+  <si>
+    <t>Forgot to ignore punctuation, spaces, and case differences</t>
+  </si>
+  <si>
+    <t>Use two pointers and compare only alphanumeric characters</t>
   </si>
 </sst>
 </file>
@@ -1684,23 +1708,51 @@
       <c r="H37" s="3"/>
     </row>
     <row r="38">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
+      <c r="A38" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>171</v>
+      </c>
       <c r="H38" s="3"/>
     </row>
     <row r="39">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
+      <c r="A39" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="H39" s="3"/>
     </row>
     <row r="40">

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="184">
   <si>
     <t>Problem Name</t>
   </si>
@@ -536,6 +536,33 @@
   </si>
   <si>
     <t>Use two pointers and compare only alphanumeric characters</t>
+  </si>
+  <si>
+    <t>Valid Parentheses</t>
+  </si>
+  <si>
+    <t>String / Stack</t>
+  </si>
+  <si>
+    <t>Tried matching brackets without a stack and forgot closing bracket must match the most recent opening bracket</t>
+  </si>
+  <si>
+    <t>Push opening brackets onto a stack. On a closing bracket, it must match the stack top.</t>
+  </si>
+  <si>
+    <t>Number of 1 Bits</t>
+  </si>
+  <si>
+    <t>Bit Manipulation / Divide &amp; Conquer</t>
+  </si>
+  <si>
+    <t>Counted bits one by one without using bit tricks</t>
+  </si>
+  <si>
+    <t>Count set bits using n &amp; 1 or repeatedly remove the lowest set bit with n &amp;= (n - 1)</t>
+  </si>
+  <si>
+    <t>Time: O(number of set bits) or O(32), Space: O(1)</t>
   </si>
 </sst>
 </file>
@@ -1756,23 +1783,51 @@
       <c r="H39" s="3"/>
     </row>
     <row r="40">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
+      <c r="A40" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="H40" s="3"/>
     </row>
     <row r="41">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
+      <c r="A41" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>183</v>
+      </c>
       <c r="H41" s="3"/>
     </row>
     <row r="42">

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="195">
   <si>
     <t>Problem Name</t>
   </si>
@@ -563,6 +563,39 @@
   </si>
   <si>
     <t>Time: O(number of set bits) or O(32), Space: O(1)</t>
+  </si>
+  <si>
+    <t>Reverse Bits</t>
+  </si>
+  <si>
+    <t>Divide and Conquer / Bit Manipulation</t>
+  </si>
+  <si>
+    <t>Tried reversing the binary string instead of using bit operations</t>
+  </si>
+  <si>
+    <t>Build the reversed number one bit at a time by shifting result left and extracting the last bit</t>
+  </si>
+  <si>
+    <t>Time: O(32), Space: O(1)</t>
+  </si>
+  <si>
+    <t>Add Two Numbers</t>
+  </si>
+  <si>
+    <t>Linked List / Math / Recursion</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Forgot to carry overflow to the next digit and mishandled different list lengths</t>
+  </si>
+  <si>
+    <t>Simulate elementary addition digit by digit while carrying overflow</t>
+  </si>
+  <si>
+    <t>Time: O(max(m,n)), Space: O(1) iterative / O(max(m,n)) recursive</t>
   </si>
 </sst>
 </file>
@@ -1831,23 +1864,51 @@
       <c r="H41" s="3"/>
     </row>
     <row r="42">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
+      <c r="A42" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>188</v>
+      </c>
       <c r="H42" s="3"/>
     </row>
     <row r="43">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
+      <c r="A43" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>194</v>
+      </c>
       <c r="H43" s="3"/>
     </row>
     <row r="44">

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="206">
   <si>
     <t>Problem Name</t>
   </si>
@@ -596,6 +596,39 @@
   </si>
   <si>
     <t>Time: O(max(m,n)), Space: O(1) iterative / O(max(m,n)) recursive</t>
+  </si>
+  <si>
+    <t>Longest Substring Without Repeating Characters</t>
+  </si>
+  <si>
+    <t>Hash Table / String / Sliding Window</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium </t>
+  </si>
+  <si>
+    <t>Restarted scanning after duplicates instead of shrinking the window</t>
+  </si>
+  <si>
+    <t>Maintain a window with unique characters using a HashSet/HashMap while expanding and shrinking</t>
+  </si>
+  <si>
+    <t>Time: O(n), Space: O(min(n, charset))</t>
+  </si>
+  <si>
+    <t>Longest Palindromic Substring</t>
+  </si>
+  <si>
+    <t>Two Pointers / String / Dynamic Programming</t>
+  </si>
+  <si>
+    <t>Tried checking every substring instead of expanding from each center</t>
+  </si>
+  <si>
+    <t>Every palindrome expands outward from its center</t>
+  </si>
+  <si>
+    <t>Time: O(n²), Space: O(1) expand-around-center</t>
   </si>
 </sst>
 </file>
@@ -1912,23 +1945,51 @@
       <c r="H43" s="3"/>
     </row>
     <row r="44">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
+      <c r="A44" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>200</v>
+      </c>
       <c r="H44" s="3"/>
     </row>
     <row r="45">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
+      <c r="A45" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>205</v>
+      </c>
       <c r="H45" s="3"/>
     </row>
   </sheetData>

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="214">
   <si>
     <t>Problem Name</t>
   </si>
@@ -629,6 +629,30 @@
   </si>
   <si>
     <t>Time: O(n²), Space: O(1) expand-around-center</t>
+  </si>
+  <si>
+    <t>Container With Most Water</t>
+  </si>
+  <si>
+    <t>Array / Two Pointers / Greedy</t>
+  </si>
+  <si>
+    <t>Tried checking every pair instead of eliminating impossible answers using two pointers</t>
+  </si>
+  <si>
+    <t>Area = width × min(height). Move the shorter line because only it can potentially increase the area.</t>
+  </si>
+  <si>
+    <t>3Sum</t>
+  </si>
+  <si>
+    <t>Used three nested loops and forgot to skip duplicates</t>
+  </si>
+  <si>
+    <t>Sort first. Fix one number, then solve a Two Sum problem with two pointers while skipping duplicates.</t>
+  </si>
+  <si>
+    <t>Time: O(n²), Space: O(1) (excluding sorting)</t>
   </si>
 </sst>
 </file>
@@ -1992,6 +2016,52 @@
       </c>
       <c r="H45" s="3"/>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="222">
   <si>
     <t>Problem Name</t>
   </si>
@@ -653,6 +653,30 @@
   </si>
   <si>
     <t>Time: O(n²), Space: O(1) (excluding sorting)</t>
+  </si>
+  <si>
+    <t>3Sum Closest</t>
+  </si>
+  <si>
+    <t>Focused on finding an exact match instead of tracking the closest sum seen so far</t>
+  </si>
+  <si>
+    <t>Sort the array, fix one number, then use two pointers while continuously updating the closest sum</t>
+  </si>
+  <si>
+    <t>Letter Combinations of a Phone Number</t>
+  </si>
+  <si>
+    <t>Hash Table / String / Backtracking</t>
+  </si>
+  <si>
+    <t>Tried generating combinations iteratively and forgot to backtrack after each recursive call</t>
+  </si>
+  <si>
+    <t>Build combinations one character at a time using DFS/backtracking and undo choices after exploring</t>
+  </si>
+  <si>
+    <t>Time: O(4ⁿ × n), Space: O(n) recursion (excluding output)</t>
   </si>
 </sst>
 </file>
@@ -2062,6 +2086,52 @@
         <v>213</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="231">
   <si>
     <t>Problem Name</t>
   </si>
@@ -677,6 +677,33 @@
   </si>
   <si>
     <t>Time: O(4ⁿ × n), Space: O(n) recursion (excluding output)</t>
+  </si>
+  <si>
+    <t>Remove Nth Node From End of List</t>
+  </si>
+  <si>
+    <t>Linked List / Two Pointers</t>
+  </si>
+  <si>
+    <t>Forgot to use a dummy node or didn’t keep the gap of n nodes between fast and slow pointers</t>
+  </si>
+  <si>
+    <t>Move fast pointer n steps ahead, then move both pointers together until fast reaches the end. Slow will stop before the node to remove.</t>
+  </si>
+  <si>
+    <t>Generate Parentheses</t>
+  </si>
+  <si>
+    <t>String / Backtracking / Dynamic Programming</t>
+  </si>
+  <si>
+    <t>Tried brute force or forgot to prune invalid parentheses early</t>
+  </si>
+  <si>
+    <t>Build the string recursively. Add ‘(’ if open &lt; n, add ‘)’ only if close &lt; open. Never generate invalid states.</t>
+  </si>
+  <si>
+    <t>Time: O(4ⁿ / √n), Space: O(n) recursion</t>
   </si>
 </sst>
 </file>
@@ -710,7 +737,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -722,6 +749,12 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2132,6 +2165,58 @@
         <v>221</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="5"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="238">
   <si>
     <t>Problem Name</t>
   </si>
@@ -704,6 +704,27 @@
   </si>
   <si>
     <t>Time: O(4ⁿ / √n), Space: O(n) recursion</t>
+  </si>
+  <si>
+    <t>Swap Nodes in Pairs</t>
+  </si>
+  <si>
+    <t>Forgot to reconnect the swapped pair after recursion; attempted swapping values instead of pointers</t>
+  </si>
+  <si>
+    <t>Swap the first two nodes, recursively solve the rest of the list, reconnect, and return the second node as the new head</t>
+  </si>
+  <si>
+    <t>Time: O(n), Space: O(n) recursive</t>
+  </si>
+  <si>
+    <t>Search in Rotated Sorted Array</t>
+  </si>
+  <si>
+    <t>Used normal binary search without first determining which half was sorted</t>
+  </si>
+  <si>
+    <t>One side of the array is always sorted. Determine the sorted half, check if the target lies within it, then continue binary search on that half</t>
   </si>
 </sst>
 </file>
@@ -2217,6 +2238,52 @@
       <c r="L51" s="4"/>
       <c r="M51" s="5"/>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="248">
   <si>
     <t>Problem Name</t>
   </si>
@@ -725,6 +725,36 @@
   </si>
   <si>
     <t>One side of the array is always sorted. Determine the sorted half, check if the target lies within it, then continue binary search on that half</t>
+  </si>
+  <si>
+    <t>Combination Sum</t>
+  </si>
+  <si>
+    <t>Array / Baktracking</t>
+  </si>
+  <si>
+    <t>Forgot to backtrack after exploring a path; didn’t allow reuse of the same candidate; didn’t prune when the sum exceeded the target</t>
+  </si>
+  <si>
+    <t>Use DFS/backtracking. Choose a number, recurse with the same index (can reuse it), subtract from the remaining target, backtrack, and stop exploring when the remaining target becomes negative</t>
+  </si>
+  <si>
+    <t>Time: O(2^t) (exponential), Space: O(target) recursion</t>
+  </si>
+  <si>
+    <t>Combination Sum II</t>
+  </si>
+  <si>
+    <t>Array / Backtracking</t>
+  </si>
+  <si>
+    <t>Generated duplicate combinations; forgot to skip duplicate values at the same recursion level; reused an element more than once</t>
+  </si>
+  <si>
+    <t>Sort the array first. Backtrack while moving to the next index after choosing a number (each number used once). Skip duplicates using if i &gt; start and candidates[i] == candidates[i-1]: continue. Prune when the current value exceeds the remaining target</t>
+  </si>
+  <si>
+    <t>Time: O(2^n) (worst case), Space: O(n) recursion</t>
   </si>
 </sst>
 </file>
@@ -2284,6 +2314,52 @@
         <v>139</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="255">
   <si>
     <t>Problem Name</t>
   </si>
@@ -755,6 +755,27 @@
   </si>
   <si>
     <t>Time: O(2^n) (worst case), Space: O(n) recursion</t>
+  </si>
+  <si>
+    <t>Permutations</t>
+  </si>
+  <si>
+    <t>Forgot to mark elements as used and remove them during backtracking; generated incomplete permutations</t>
+  </si>
+  <si>
+    <t>Build permutations one element at a time. Track used elements with a visited array, choose an unused number, recurse, then backtrack by unmarking it</t>
+  </si>
+  <si>
+    <t>Time: O(n × n!), Space: O(n) recursion + visited</t>
+  </si>
+  <si>
+    <t>Permutations II</t>
+  </si>
+  <si>
+    <t>Generated duplicate permutations; forgot to sort first and skip duplicate values at the same recursion level</t>
+  </si>
+  <si>
+    <t>Sort the array first. Use a visited array and skip duplicates with if i &gt; 0 and nums[i] == nums[i-1] and not visited[i-1]: continue</t>
   </si>
 </sst>
 </file>
@@ -2360,6 +2381,54 @@
         <v>247</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="H56" s="3"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="H57" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="264">
   <si>
     <t>Problem Name</t>
   </si>
@@ -776,6 +776,33 @@
   </si>
   <si>
     <t>Sort the array first. Use a visited array and skip duplicates with if i &gt; 0 and nums[i] == nums[i-1] and not visited[i-1]: continue</t>
+  </si>
+  <si>
+    <t>Rotate Image</t>
+  </si>
+  <si>
+    <t>Array / Math / Matrix</t>
+  </si>
+  <si>
+    <t>Tried using extra space instead of rotating in-place; forgot the transpose + reverse trick</t>
+  </si>
+  <si>
+    <t>Rotate the matrix 90° clockwise by first transposing it, then reversing each row. This performs the rotation in-place</t>
+  </si>
+  <si>
+    <t>Time: O(n²), Space: O(1)</t>
+  </si>
+  <si>
+    <t>Maximum Subarray</t>
+  </si>
+  <si>
+    <t>Array / Divide and Conquer / Dynamic Programming</t>
+  </si>
+  <si>
+    <t>Restarted the sum too late; forgot that a negative running sum hurts future subarrays</t>
+  </si>
+  <si>
+    <t>Use Kadane’s Algorithm. At each position, decide whether to start a new subarray or extend the current one. Keep track of the largest sum seen so far</t>
   </si>
 </sst>
 </file>
@@ -2429,6 +2456,52 @@
       </c>
       <c r="H57" s="3"/>
     </row>
+    <row r="58">
+      <c r="A58" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="272">
   <si>
     <t>Problem Name</t>
   </si>
@@ -803,6 +803,30 @@
   </si>
   <si>
     <t>Use Kadane’s Algorithm. At each position, decide whether to start a new subarray or extend the current one. Keep track of the largest sum seen so far</t>
+  </si>
+  <si>
+    <t>Spiral Matrix</t>
+  </si>
+  <si>
+    <t>Forgot to update the boundaries after traversing each side; revisited elements by not checking boundary conditions</t>
+  </si>
+  <si>
+    <t>Maintain four boundaries (top, bottom, left, right). Traverse right, down, left, and up while shrinking the boundaries after each pass</t>
+  </si>
+  <si>
+    <t>Time: O(m × n), Space: O(1) (excluding output)</t>
+  </si>
+  <si>
+    <t>Jump Game</t>
+  </si>
+  <si>
+    <t>Array / Dynamic Programming / Greedy</t>
+  </si>
+  <si>
+    <t>Focused on maximizing jump length instead of maintaining the farthest reachable index; assumed every large jump was optimal</t>
+  </si>
+  <si>
+    <t>Keep track of the farthest index reachable. If the current index is ever beyond that reach, return False. Otherwise continuously update the farthest reachable position</t>
   </si>
 </sst>
 </file>
@@ -2502,6 +2526,52 @@
         <v>28</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="280">
   <si>
     <t>Problem Name</t>
   </si>
@@ -827,6 +827,30 @@
   </si>
   <si>
     <t>Keep track of the farthest index reachable. If the current index is ever beyond that reach, return False. Otherwise continuously update the farthest reachable position</t>
+  </si>
+  <si>
+    <t>Merge Intervals</t>
+  </si>
+  <si>
+    <t>Forgot to sort intervals first; treated overlapping intervals as separate instead of merging them</t>
+  </si>
+  <si>
+    <t>Sort intervals by start time. Compare each interval with the last merged interval—if they overlap, extend the end; otherwise add a new interval</t>
+  </si>
+  <si>
+    <t>Time: O(n log n), Space: O(n) (or O(1) extra if modifying in place)</t>
+  </si>
+  <si>
+    <t>Insert Interval</t>
+  </si>
+  <si>
+    <t>Array</t>
+  </si>
+  <si>
+    <t>Forgot to merge the new interval with overlapping intervals; inserted it without checking for overlap</t>
+  </si>
+  <si>
+    <t>Add all intervals before the new interval, merge every overlapping interval into the new one, then append the remaining intervals</t>
   </si>
 </sst>
 </file>
@@ -2572,6 +2596,52 @@
         <v>28</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="288">
   <si>
     <t>Problem Name</t>
   </si>
@@ -851,6 +851,30 @@
   </si>
   <si>
     <t>Add all intervals before the new interval, merge every overlapping interval into the new one, then append the remaining intervals</t>
+  </si>
+  <si>
+    <t>Rotate List</t>
+  </si>
+  <si>
+    <t>Forgot to handle k &gt; length; didn’t reconnect the tail to the head before breaking the list</t>
+  </si>
+  <si>
+    <t>Compute the list length, reduce k using modulo, temporarily make the list circular, then break it at the new tail</t>
+  </si>
+  <si>
+    <t>Unique Paths</t>
+  </si>
+  <si>
+    <t>Math / Dynamic Programming / Combinatorics</t>
+  </si>
+  <si>
+    <t>Tried brute force recursion; forgot each cell only depends on the top and left cells</t>
+  </si>
+  <si>
+    <t>Either use DP where dp[i][j] = dp[i-1][j] + dp[i][j-1] or use the combinatorics formula C(m+n-2, m-1)</t>
+  </si>
+  <si>
+    <t>Time: O(m × n) DP or O(min(m,n)) Math, Space: O(n) DP or O(1) Math</t>
   </si>
 </sst>
 </file>
@@ -2642,6 +2666,52 @@
         <v>13</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="298">
   <si>
     <t>Problem Name</t>
   </si>
@@ -875,6 +875,36 @@
   </si>
   <si>
     <t>Time: O(m × n) DP or O(min(m,n)) Math, Space: O(n) DP or O(1) Math</t>
+  </si>
+  <si>
+    <t>Set Matrix Zeroes</t>
+  </si>
+  <si>
+    <t>Array / Hash Table / Matrix</t>
+  </si>
+  <si>
+    <t>Modified rows and columns immediately after finding a zero, causing extra zeros to spread incorrectly</t>
+  </si>
+  <si>
+    <t>Use the first row and first column as marker arrays (or separate row/column sets), then perform a second pass to zero the matrix</t>
+  </si>
+  <si>
+    <t>Time: O(m × n), Space: O(1) (optimal) or O(m + n) with sets</t>
+  </si>
+  <si>
+    <t>Search a 2D Matrix</t>
+  </si>
+  <si>
+    <t>Array / Binary Search / Matrix</t>
+  </si>
+  <si>
+    <t>Treated each row independently instead of recognizing the entire matrix is sorted as one flattened array</t>
+  </si>
+  <si>
+    <t>Perform binary search on the virtual 1D array by mapping indices back to row and column</t>
+  </si>
+  <si>
+    <t>Time: O(log(m × n)), Space: O(1)</t>
   </si>
 </sst>
 </file>
@@ -2712,6 +2742,52 @@
         <v>287</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="306">
   <si>
     <t>Problem Name</t>
   </si>
@@ -905,6 +905,30 @@
   </si>
   <si>
     <t>Time: O(log(m × n)), Space: O(1)</t>
+  </si>
+  <si>
+    <t>Sort Colors</t>
+  </si>
+  <si>
+    <t>Initially used sorting (O(n log n)); forgot the optimal one-pass Dutch National Flag algorithm</t>
+  </si>
+  <si>
+    <t>Maintain three pointers (low, mid, high) to partition 0s, 1s, and 2s in one traversal</t>
+  </si>
+  <si>
+    <t>Combinations</t>
+  </si>
+  <si>
+    <t>Backtracking</t>
+  </si>
+  <si>
+    <t>Forgot to backtrack after recursive calls; generated duplicate or incomplete combinations</t>
+  </si>
+  <si>
+    <t>Build combinations recursively by choosing the next number, exploring, then removing it before trying the next option</t>
+  </si>
+  <si>
+    <t>Time: O(C(n,k) × k), Space: O(k) (excluding output)</t>
   </si>
 </sst>
 </file>
@@ -2788,6 +2812,52 @@
         <v>297</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="316">
   <si>
     <t>Problem Name</t>
   </si>
@@ -929,6 +929,36 @@
   </si>
   <si>
     <t>Time: O(C(n,k) × k), Space: O(k) (excluding output)</t>
+  </si>
+  <si>
+    <t>Subsets</t>
+  </si>
+  <si>
+    <t>Array / Backtracking / Bit Manipulation</t>
+  </si>
+  <si>
+    <t>Forgot that every recursive level represents a decision (take or don’t take); modified the same list without backtracking</t>
+  </si>
+  <si>
+    <t>At each element, either include it or skip it. This generates every possible subset (the power set)</t>
+  </si>
+  <si>
+    <t>Time: O(n × 2ⁿ), Space: O(n) (excluding output)</t>
+  </si>
+  <si>
+    <t>Word Search</t>
+  </si>
+  <si>
+    <t>Array / String / Backtracking / DFS / Matrix</t>
+  </si>
+  <si>
+    <t>Forgot to mark cells as visited, causing reuse of the same cell; didn’t restore the cell after recursion</t>
+  </si>
+  <si>
+    <t>Perform DFS from each cell, marking visited cells temporarily and backtracking after exploring all directions</t>
+  </si>
+  <si>
+    <t>Time: O(m × n × 4ᴸ), Space: O(L)</t>
   </si>
 </sst>
 </file>
@@ -2858,6 +2888,52 @@
         <v>305</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="326">
   <si>
     <t>Problem Name</t>
   </si>
@@ -959,6 +959,36 @@
   </si>
   <si>
     <t>Time: O(m × n × 4ᴸ), Space: O(L)</t>
+  </si>
+  <si>
+    <t>Search in Rotated Sorted Array II</t>
+  </si>
+  <si>
+    <t>Binary Search, Modified Binary Search</t>
+  </si>
+  <si>
+    <t>Forgot that duplicates can prevent identifying the sorted half and used normal rotated binary search.</t>
+  </si>
+  <si>
+    <t>If duplicates hide which half is sorted (nums[left] == nums[mid] == nums[right]), shrink both ends. Otherwise perform normal rotated binary search.</t>
+  </si>
+  <si>
+    <t>Average: O(log n), Worst: O(n) time, O(1) space</t>
+  </si>
+  <si>
+    <t>Subsets II</t>
+  </si>
+  <si>
+    <t>Array, Backtracking, Bit Manipulation</t>
+  </si>
+  <si>
+    <t>Forgot to sort and generated duplicate subsets.</t>
+  </si>
+  <si>
+    <t>Sort first, then skip duplicate values at the same recursion level.</t>
+  </si>
+  <si>
+    <t>O(n·2ⁿ) time, O(n) space</t>
   </si>
 </sst>
 </file>
@@ -2934,6 +2964,52 @@
         <v>315</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="334">
   <si>
     <t>Problem Name</t>
   </si>
@@ -989,6 +989,30 @@
   </si>
   <si>
     <t>O(n·2ⁿ) time, O(n) space</t>
+  </si>
+  <si>
+    <t>Decode Ways</t>
+  </si>
+  <si>
+    <t>String, Dynamic Programming</t>
+  </si>
+  <si>
+    <t>Tried recursive/backtracking solution instead of recognizing overlapping subproblems. Forgot to handle invalid zeros.</t>
+  </si>
+  <si>
+    <t>Let dp[i] represent the number of ways to decode the string starting at index i. At each position, try taking one digit and, if valid (10–26), two digits.</t>
+  </si>
+  <si>
+    <t>Time: O(n), Space: O(n) (O(1) optimized)</t>
+  </si>
+  <si>
+    <t>Reverse Linked List II</t>
+  </si>
+  <si>
+    <t>Lost track of the node before the reversal and didn’t reconnect the reversed section correctly.</t>
+  </si>
+  <si>
+    <t>Find the node before left, reverse only the sublist [left, right], then reconnect the three parts.</t>
   </si>
 </sst>
 </file>
@@ -1022,7 +1046,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1040,6 +1064,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3010,6 +3037,52 @@
         <v>325</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="343">
   <si>
     <t>Problem Name</t>
   </si>
@@ -1013,6 +1013,33 @@
   </si>
   <si>
     <t>Find the node before left, reverse only the sublist [left, right], then reconnect the three parts.</t>
+  </si>
+  <si>
+    <t>Validate Binary Search Tree</t>
+  </si>
+  <si>
+    <t>Tree, Depth-First Search, Binary Search Tree</t>
+  </si>
+  <si>
+    <t>Only compared each node with its immediate children instead of enforcing valid min/max bounds for the entire subtree.</t>
+  </si>
+  <si>
+    <t>Every node must satisfy min &lt; node.val &lt; max inherited from all ancestors, not just its parent.</t>
+  </si>
+  <si>
+    <t>Time: O(n), Space: O(h) (O(n) worst-case)</t>
+  </si>
+  <si>
+    <t>Binary Tree Level Order Traversal</t>
+  </si>
+  <si>
+    <t>Tree, Breadth-First Search, Binary Tree</t>
+  </si>
+  <si>
+    <t>Processed nodes one at a time instead of grouping nodes by level. Forgot to store the queue size before each level.</t>
+  </si>
+  <si>
+    <t>Use a queue (BFS). Before processing a level, save the queue size so exactly one level is processed at a time.</t>
   </si>
 </sst>
 </file>
@@ -3083,6 +3110,52 @@
         <v>28</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="350">
   <si>
     <t>Problem Name</t>
   </si>
@@ -1040,6 +1040,27 @@
   </si>
   <si>
     <t>Use a queue (BFS). Before processing a level, save the queue size so exactly one level is processed at a time.</t>
+  </si>
+  <si>
+    <t>Binary Tree Zigzag Level Order Traversal</t>
+  </si>
+  <si>
+    <t>Used normal level-order traversal and forgot to reverse every other level.</t>
+  </si>
+  <si>
+    <t>Perform BFS level by level. Alternate the direction of insertion (left→right, then right→left).</t>
+  </si>
+  <si>
+    <t>Construct Binary Tree from Preorder and Inorder Traversal</t>
+  </si>
+  <si>
+    <t>Tree, Divide &amp; Conquer, Hash Table</t>
+  </si>
+  <si>
+    <t>Repeatedly searched the inorder array, causing O(n²), and mixed up subtree boundaries.</t>
+  </si>
+  <si>
+    <t>Preorder gives the root first. Use a hashmap of inorder indices to split left/right subtrees efficiently.</t>
   </si>
 </sst>
 </file>
@@ -3156,6 +3177,52 @@
         <v>13</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="358">
   <si>
     <t>Problem Name</t>
   </si>
@@ -1061,6 +1061,30 @@
   </si>
   <si>
     <t>Preorder gives the root first. Use a hashmap of inorder indices to split left/right subtrees efficiently.</t>
+  </si>
+  <si>
+    <t>Binary Tree Level Order Traversal II</t>
+  </si>
+  <si>
+    <t>Built the levels from top to bottom and reversed the answer at the wrong time.</t>
+  </si>
+  <si>
+    <t>Perform normal BFS, collect levels, then reverse the final list (or prepend each level).</t>
+  </si>
+  <si>
+    <t>Path Sum II</t>
+  </si>
+  <si>
+    <t>Tree, Depth-First Search, Backtracking, Binary Tree</t>
+  </si>
+  <si>
+    <t>Forgot to backtrack (pop) after recursion, causing paths to contain extra nodes.</t>
+  </si>
+  <si>
+    <t>DFS while tracking the current path and remaining target. At a leaf, save a copy if the sum matches.</t>
+  </si>
+  <si>
+    <t>Time: O(n²) worst case, Space: O(h)</t>
   </si>
 </sst>
 </file>
@@ -3178,49 +3202,95 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="s">
+      <c r="A78" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E78" s="5" t="s">
+      <c r="C78" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="F78" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="G78" s="1" t="s">
+      <c r="G78" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="s">
+      <c r="A79" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E79" s="1" t="s">
+      <c r="C79" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E79" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="F79" s="1" t="s">
+      <c r="F79" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="G79" s="1" t="s">
+      <c r="G79" s="2" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>357</v>
       </c>
     </row>
   </sheetData>

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="367">
   <si>
     <t>Problem Name</t>
   </si>
@@ -1085,6 +1085,33 @@
   </si>
   <si>
     <t>Time: O(n²) worst case, Space: O(h)</t>
+  </si>
+  <si>
+    <t>Longest Consecutive Sequence</t>
+  </si>
+  <si>
+    <t>Array, Hash Table</t>
+  </si>
+  <si>
+    <t>Tried sorting first (O(n log n)) instead of identifying sequence starts with a hash set.</t>
+  </si>
+  <si>
+    <t>Put all numbers in a hash set. Only start counting from numbers where num - 1 is not in the set.</t>
+  </si>
+  <si>
+    <t>Palindrome Partitioning</t>
+  </si>
+  <si>
+    <t>String, Backtracking</t>
+  </si>
+  <si>
+    <t>Didn’t backtrack correctly and repeatedly checked the same substrings for palindrome.</t>
+  </si>
+  <si>
+    <t>Try every prefix that is a palindrome, recurse on the remaining suffix, then backtrack.</t>
+  </si>
+  <si>
+    <t>Time: O(n · 2ⁿ), Space: O(n) recursion (excluding output)</t>
   </si>
 </sst>
 </file>
@@ -3293,6 +3320,50 @@
         <v>357</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B83" s="3"/>
+      <c r="C83" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Leetcode  (1).xlsx
+++ b/Leetcode  (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="376">
   <si>
     <t>Problem Name</t>
   </si>
@@ -1112,6 +1112,33 @@
   </si>
   <si>
     <t>Time: O(n · 2ⁿ), Space: O(n) recursion (excluding output)</t>
+  </si>
+  <si>
+    <t>Gas Station</t>
+  </si>
+  <si>
+    <t>Greedy</t>
+  </si>
+  <si>
+    <t>Tried checking every starting station instead of realizing there is only one possible valid start after a failure.</t>
+  </si>
+  <si>
+    <t>If total gas is less than total cost, return -1. Otherwise, greedily reset the start whenever the current tank becomes negative.</t>
+  </si>
+  <si>
+    <t>Word Break</t>
+  </si>
+  <si>
+    <t>Dynamic Programming</t>
+  </si>
+  <si>
+    <t>Tried brute-force recursion without memoization/DP, causing repeated work.</t>
+  </si>
+  <si>
+    <t>Let dp[i] represent whether the prefix ending at i can be formed. Build the answer using previously computed prefixes.</t>
+  </si>
+  <si>
+    <t>Time: O(n²), Space: O(n)</t>
   </si>
 </sst>
 </file>
@@ -3364,6 +3391,52 @@
         <v>366</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
